--- a/rcads/data/xls/11_InstrumentComponents.xlsx
+++ b/rcads/data/xls/11_InstrumentComponents.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_11_InstrumentComponents"/>
   </sheets>
   <definedNames>
-    <definedName name="_11_InstrumentComponents">'_11_InstrumentComponents'!$A$1:$E$600</definedName>
+    <definedName name="_11_InstrumentComponents">'_11_InstrumentComponents'!$A$1:$E$625</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E600"/>
+  <dimension ref="A1:E625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -11375,6 +11375,481 @@
         <v>0</v>
       </c>
     </row>
+    <row outlineLevel="0" r="601">
+      <c r="A601" s="0">
+        <v>609</v>
+      </c>
+      <c r="B601" s="0">
+        <v>154</v>
+      </c>
+      <c r="C601" s="0">
+        <v>2</v>
+      </c>
+      <c r="D601" s="0" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E601" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="602">
+      <c r="A602" s="0">
+        <v>610</v>
+      </c>
+      <c r="B602" s="0">
+        <v>154</v>
+      </c>
+      <c r="C602" s="0">
+        <v>1</v>
+      </c>
+      <c r="D602" s="0" t="inlineStr">
+        <is>
+          <t>Nome/Identificativo</t>
+        </is>
+      </c>
+      <c r="E602" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="603">
+      <c r="A603" s="0">
+        <v>611</v>
+      </c>
+      <c r="B603" s="0">
+        <v>154</v>
+      </c>
+      <c r="C603" s="0">
+        <v>4</v>
+      </c>
+      <c r="D603" s="0" t="inlineStr">
+        <is>
+          <t>Per favore, indica la parola che meglio rappresenta con che frequenza ciascuna delle seguenti cose ti succede. Non ci sono risposte giuste o sbagliate.</t>
+        </is>
+      </c>
+      <c r="E603" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="604">
+      <c r="A604" s="0">
+        <v>612</v>
+      </c>
+      <c r="B604" s="0">
+        <v>155</v>
+      </c>
+      <c r="C604" s="0">
+        <v>2</v>
+      </c>
+      <c r="D604" s="0" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E604" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="605">
+      <c r="A605" s="0">
+        <v>613</v>
+      </c>
+      <c r="B605" s="0">
+        <v>155</v>
+      </c>
+      <c r="C605" s="0">
+        <v>1</v>
+      </c>
+      <c r="D605" s="0" t="inlineStr">
+        <is>
+          <t>Nome/Identificativo</t>
+        </is>
+      </c>
+      <c r="E605" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="606">
+      <c r="A606" s="0">
+        <v>614</v>
+      </c>
+      <c r="B606" s="0">
+        <v>155</v>
+      </c>
+      <c r="C606" s="0">
+        <v>4</v>
+      </c>
+      <c r="D606" s="0" t="inlineStr">
+        <is>
+          <t>Prego indichi le parole che mostrano con che frequenza ciascuna delle seguenti esperienze capitano al suo bambino/ragazzo.</t>
+        </is>
+      </c>
+      <c r="E606" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="607">
+      <c r="A607" s="0">
+        <v>615</v>
+      </c>
+      <c r="B607" s="0">
+        <v>155</v>
+      </c>
+      <c r="C607" s="0">
+        <v>6</v>
+      </c>
+      <c r="D607" s="0" t="inlineStr">
+        <is>
+          <t>Relazione con il bambino/ragazzo</t>
+        </is>
+      </c>
+      <c r="E607" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="608">
+      <c r="A608" s="0">
+        <v>616</v>
+      </c>
+      <c r="B608" s="0">
+        <v>172</v>
+      </c>
+      <c r="C608" s="0">
+        <v>2</v>
+      </c>
+      <c r="D608" s="0" t="inlineStr">
+        <is>
+          <t>Usuku</t>
+        </is>
+      </c>
+      <c r="E608" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="609">
+      <c r="A609" s="0">
+        <v>617</v>
+      </c>
+      <c r="B609" s="0">
+        <v>172</v>
+      </c>
+      <c r="C609" s="0">
+        <v>1</v>
+      </c>
+      <c r="D609" s="0" t="inlineStr">
+        <is>
+          <t>Igama</t>
+        </is>
+      </c>
+      <c r="E609" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="610">
+      <c r="A610" s="0">
+        <v>618</v>
+      </c>
+      <c r="B610" s="0">
+        <v>172</v>
+      </c>
+      <c r="C610" s="0">
+        <v>4</v>
+      </c>
+      <c r="D610" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ubeke indilinga uzungeze igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki kuwe. Azikho izimpendulo ezilungile noma ezingalungile.</t>
+        </is>
+      </c>
+      <c r="E610" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="611">
+      <c r="A611" s="0">
+        <v>619</v>
+      </c>
+      <c r="B611" s="0">
+        <v>173</v>
+      </c>
+      <c r="C611" s="0">
+        <v>2</v>
+      </c>
+      <c r="D611" s="0" t="inlineStr">
+        <is>
+          <t>Usuku</t>
+        </is>
+      </c>
+      <c r="E611" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="612">
+      <c r="A612" s="0">
+        <v>620</v>
+      </c>
+      <c r="B612" s="0">
+        <v>173</v>
+      </c>
+      <c r="C612" s="0">
+        <v>1</v>
+      </c>
+      <c r="D612" s="0" t="inlineStr">
+        <is>
+          <t>Igama</t>
+        </is>
+      </c>
+      <c r="E612" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="613">
+      <c r="A613" s="0">
+        <v>621</v>
+      </c>
+      <c r="B613" s="0">
+        <v>173</v>
+      </c>
+      <c r="C613" s="0">
+        <v>4</v>
+      </c>
+      <c r="D613" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ubeke indilinga uzungeze igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki enganeni yakho.</t>
+        </is>
+      </c>
+      <c r="E613" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="614">
+      <c r="A614" s="0">
+        <v>622</v>
+      </c>
+      <c r="B614" s="0">
+        <v>173</v>
+      </c>
+      <c r="C614" s="0">
+        <v>6</v>
+      </c>
+      <c r="D614" s="0" t="inlineStr">
+        <is>
+          <t>Ubuhlobo Nengane</t>
+        </is>
+      </c>
+      <c r="E614" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="615">
+      <c r="A615" s="0">
+        <v>623</v>
+      </c>
+      <c r="B615" s="0">
+        <v>172</v>
+      </c>
+      <c r="C615" s="0">
+        <v>5</v>
+      </c>
+      <c r="D615" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ukhethe igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki kuwe. Azikho izimpendulo ezilungile noma ezingalungile.</t>
+        </is>
+      </c>
+      <c r="E615" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="616">
+      <c r="A616" s="0">
+        <v>624</v>
+      </c>
+      <c r="B616" s="0">
+        <v>173</v>
+      </c>
+      <c r="C616" s="0">
+        <v>5</v>
+      </c>
+      <c r="D616" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ukhethe igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki enganeni yakho.</t>
+        </is>
+      </c>
+      <c r="E616" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="617">
+      <c r="A617" s="0">
+        <v>625</v>
+      </c>
+      <c r="B617" s="0">
+        <v>174</v>
+      </c>
+      <c r="C617" s="0">
+        <v>2</v>
+      </c>
+      <c r="D617" s="0" t="inlineStr">
+        <is>
+          <t>Usuku</t>
+        </is>
+      </c>
+      <c r="E617" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="618">
+      <c r="A618" s="0">
+        <v>626</v>
+      </c>
+      <c r="B618" s="0">
+        <v>174</v>
+      </c>
+      <c r="C618" s="0">
+        <v>1</v>
+      </c>
+      <c r="D618" s="0" t="inlineStr">
+        <is>
+          <t>Igama</t>
+        </is>
+      </c>
+      <c r="E618" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="619">
+      <c r="A619" s="0">
+        <v>627</v>
+      </c>
+      <c r="B619" s="0">
+        <v>174</v>
+      </c>
+      <c r="C619" s="0">
+        <v>4</v>
+      </c>
+      <c r="D619" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ubeke indilinga uzungeze igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki kuwe. Azikho izimpendulo ezilungile noma ezingalungile</t>
+        </is>
+      </c>
+      <c r="E619" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="620">
+      <c r="A620" s="0">
+        <v>628</v>
+      </c>
+      <c r="B620" s="0">
+        <v>174</v>
+      </c>
+      <c r="C620" s="0">
+        <v>5</v>
+      </c>
+      <c r="D620" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ukhethe igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki kuwe. Azikho izimpendulo ezilungile noma ezingalungile.</t>
+        </is>
+      </c>
+      <c r="E620" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="621">
+      <c r="A621" s="0">
+        <v>629</v>
+      </c>
+      <c r="B621" s="0">
+        <v>175</v>
+      </c>
+      <c r="C621" s="0">
+        <v>2</v>
+      </c>
+      <c r="D621" s="0" t="inlineStr">
+        <is>
+          <t>Usuku</t>
+        </is>
+      </c>
+      <c r="E621" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="622">
+      <c r="A622" s="0">
+        <v>630</v>
+      </c>
+      <c r="B622" s="0">
+        <v>175</v>
+      </c>
+      <c r="C622" s="0">
+        <v>1</v>
+      </c>
+      <c r="D622" s="0" t="inlineStr">
+        <is>
+          <t>Igama</t>
+        </is>
+      </c>
+      <c r="E622" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="623">
+      <c r="A623" s="0">
+        <v>631</v>
+      </c>
+      <c r="B623" s="0">
+        <v>175</v>
+      </c>
+      <c r="C623" s="0">
+        <v>4</v>
+      </c>
+      <c r="D623" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ubeke indilinga uzungeze igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki enganeni yakho.</t>
+        </is>
+      </c>
+      <c r="E623" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="624">
+      <c r="A624" s="0">
+        <v>632</v>
+      </c>
+      <c r="B624" s="0">
+        <v>175</v>
+      </c>
+      <c r="C624" s="0">
+        <v>5</v>
+      </c>
+      <c r="D624" s="0" t="inlineStr">
+        <is>
+          <t>Sicela ukhethe igama elibonisa ukuthi ngayinye yalezi zinto zenzeka kangaki enganeni yakho.</t>
+        </is>
+      </c>
+      <c r="E624" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="625">
+      <c r="A625" s="0">
+        <v>633</v>
+      </c>
+      <c r="B625" s="0">
+        <v>175</v>
+      </c>
+      <c r="C625" s="0">
+        <v>6</v>
+      </c>
+      <c r="D625" s="0" t="inlineStr">
+        <is>
+          <t>Ubuhlobo Nengane</t>
+        </is>
+      </c>
+      <c r="E625" s="0">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/rcads/data/xls/11_InstrumentComponents.xlsx
+++ b/rcads/data/xls/11_InstrumentComponents.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_11_InstrumentComponents"/>
   </sheets>
   <definedNames>
-    <definedName name="_11_InstrumentComponents">'_11_InstrumentComponents'!$A$1:$E$625</definedName>
+    <definedName name="_11_InstrumentComponents">'_11_InstrumentComponents'!$A$1:$E$661</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E625"/>
+  <dimension ref="A1:E661"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -11850,6 +11850,690 @@
         <v>4</v>
       </c>
     </row>
+    <row outlineLevel="0" r="626">
+      <c r="A626" s="0">
+        <v>634</v>
+      </c>
+      <c r="B626" s="0">
+        <v>158</v>
+      </c>
+      <c r="C626" s="0">
+        <v>2</v>
+      </c>
+      <c r="D626" s="0" t="inlineStr">
+        <is>
+          <t>Tsiku</t>
+        </is>
+      </c>
+      <c r="E626" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="627">
+      <c r="A627" s="0">
+        <v>635</v>
+      </c>
+      <c r="B627" s="0">
+        <v>158</v>
+      </c>
+      <c r="C627" s="0">
+        <v>1</v>
+      </c>
+      <c r="D627" s="0" t="inlineStr">
+        <is>
+          <t>Dzina/Chizindikiro</t>
+        </is>
+      </c>
+      <c r="E627" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="628">
+      <c r="A628" s="0">
+        <v>636</v>
+      </c>
+      <c r="B628" s="0">
+        <v>158</v>
+      </c>
+      <c r="C628" s="0">
+        <v>4</v>
+      </c>
+      <c r="D628" s="0" t="inlineStr">
+        <is>
+          <t>Chonde zungulizani mawu amene akuwonetsa ndikangazi zinthu izi zachitika kwa inu. Palibe yankho lolondola kapena lokhonza.</t>
+        </is>
+      </c>
+      <c r="E628" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="629">
+      <c r="A629" s="0">
+        <v>637</v>
+      </c>
+      <c r="B629" s="0">
+        <v>160</v>
+      </c>
+      <c r="C629" s="0">
+        <v>2</v>
+      </c>
+      <c r="D629" s="0" t="inlineStr">
+        <is>
+          <t>Tsiku</t>
+        </is>
+      </c>
+      <c r="E629" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="630">
+      <c r="A630" s="0">
+        <v>638</v>
+      </c>
+      <c r="B630" s="0">
+        <v>160</v>
+      </c>
+      <c r="C630" s="0">
+        <v>1</v>
+      </c>
+      <c r="D630" s="0" t="inlineStr">
+        <is>
+          <t>Dzina/Chizindikiro</t>
+        </is>
+      </c>
+      <c r="E630" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="631">
+      <c r="A631" s="0">
+        <v>639</v>
+      </c>
+      <c r="B631" s="0">
+        <v>160</v>
+      </c>
+      <c r="C631" s="0">
+        <v>4</v>
+      </c>
+      <c r="D631" s="0" t="inlineStr">
+        <is>
+          <t>Chonde zungulizani mawu amene akuwonetsa ndikangazi zinthu izi zachitika kwa inu. Palibe yankho lolondola kapena lokhonza.</t>
+        </is>
+      </c>
+      <c r="E631" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="632">
+      <c r="A632" s="0">
+        <v>640</v>
+      </c>
+      <c r="B632" s="0">
+        <v>159</v>
+      </c>
+      <c r="C632" s="0">
+        <v>2</v>
+      </c>
+      <c r="D632" s="0" t="inlineStr">
+        <is>
+          <t>Tsiku</t>
+        </is>
+      </c>
+      <c r="E632" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="633">
+      <c r="A633" s="0">
+        <v>641</v>
+      </c>
+      <c r="B633" s="0">
+        <v>159</v>
+      </c>
+      <c r="C633" s="0">
+        <v>1</v>
+      </c>
+      <c r="D633" s="0" t="inlineStr">
+        <is>
+          <t>Dzina/Chizindikiro</t>
+        </is>
+      </c>
+      <c r="E633" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="634">
+      <c r="A634" s="0">
+        <v>642</v>
+      </c>
+      <c r="B634" s="0">
+        <v>159</v>
+      </c>
+      <c r="C634" s="0">
+        <v>4</v>
+      </c>
+      <c r="D634" s="0" t="inlineStr">
+        <is>
+          <t>Chonde zungulizani mawu amene akuwonetsa kuti izi zachitika kangati kwa mwana wanu.</t>
+        </is>
+      </c>
+      <c r="E634" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="635">
+      <c r="A635" s="0">
+        <v>643</v>
+      </c>
+      <c r="B635" s="0">
+        <v>159</v>
+      </c>
+      <c r="C635" s="0">
+        <v>6</v>
+      </c>
+      <c r="D635" s="0" t="inlineStr">
+        <is>
+          <t>Ubale ndi mwana</t>
+        </is>
+      </c>
+      <c r="E635" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="636">
+      <c r="A636" s="0">
+        <v>644</v>
+      </c>
+      <c r="B636" s="0">
+        <v>161</v>
+      </c>
+      <c r="C636" s="0">
+        <v>2</v>
+      </c>
+      <c r="D636" s="0" t="inlineStr">
+        <is>
+          <t>Tsiku</t>
+        </is>
+      </c>
+      <c r="E636" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="637">
+      <c r="A637" s="0">
+        <v>645</v>
+      </c>
+      <c r="B637" s="0">
+        <v>161</v>
+      </c>
+      <c r="C637" s="0">
+        <v>1</v>
+      </c>
+      <c r="D637" s="0" t="inlineStr">
+        <is>
+          <t>Dzina/Chizindikiro</t>
+        </is>
+      </c>
+      <c r="E637" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="638">
+      <c r="A638" s="0">
+        <v>646</v>
+      </c>
+      <c r="B638" s="0">
+        <v>161</v>
+      </c>
+      <c r="C638" s="0">
+        <v>4</v>
+      </c>
+      <c r="D638" s="0" t="inlineStr">
+        <is>
+          <t>Chonde zungulizani mawu amene akuwonetsa kuti izi zachitika kangati kwa mwana wanu.</t>
+        </is>
+      </c>
+      <c r="E638" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="639">
+      <c r="A639" s="0">
+        <v>647</v>
+      </c>
+      <c r="B639" s="0">
+        <v>161</v>
+      </c>
+      <c r="C639" s="0">
+        <v>6</v>
+      </c>
+      <c r="D639" s="0" t="inlineStr">
+        <is>
+          <t>Ubale ndi mwana</t>
+        </is>
+      </c>
+      <c r="E639" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="640">
+      <c r="A640" s="0">
+        <v>648</v>
+      </c>
+      <c r="B640" s="0">
+        <v>170</v>
+      </c>
+      <c r="C640" s="0">
+        <v>2</v>
+      </c>
+      <c r="D640" s="0" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E640" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="641">
+      <c r="A641" s="0">
+        <v>649</v>
+      </c>
+      <c r="B641" s="0">
+        <v>170</v>
+      </c>
+      <c r="C641" s="0">
+        <v>1</v>
+      </c>
+      <c r="D641" s="0" t="inlineStr">
+        <is>
+          <t>Nome/Identificativo</t>
+        </is>
+      </c>
+      <c r="E641" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="642">
+      <c r="A642" s="0">
+        <v>650</v>
+      </c>
+      <c r="B642" s="0">
+        <v>170</v>
+      </c>
+      <c r="C642" s="0">
+        <v>4</v>
+      </c>
+      <c r="D642" s="0" t="inlineStr">
+        <is>
+          <t>Per favore, indica la parola che meglio rappresenta con che frequenza ciascuna delle seguenti cose ti succede. Non ci sono risposte giuste o sbagliate.</t>
+        </is>
+      </c>
+      <c r="E642" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="643">
+      <c r="A643" s="0">
+        <v>651</v>
+      </c>
+      <c r="B643" s="0">
+        <v>171</v>
+      </c>
+      <c r="C643" s="0">
+        <v>2</v>
+      </c>
+      <c r="D643" s="0" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E643" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="644">
+      <c r="A644" s="0">
+        <v>652</v>
+      </c>
+      <c r="B644" s="0">
+        <v>171</v>
+      </c>
+      <c r="C644" s="0">
+        <v>1</v>
+      </c>
+      <c r="D644" s="0" t="inlineStr">
+        <is>
+          <t>Nome/Identificativo</t>
+        </is>
+      </c>
+      <c r="E644" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="645">
+      <c r="A645" s="0">
+        <v>653</v>
+      </c>
+      <c r="B645" s="0">
+        <v>171</v>
+      </c>
+      <c r="C645" s="0">
+        <v>4</v>
+      </c>
+      <c r="D645" s="0" t="inlineStr">
+        <is>
+          <t>Prego indichi le parole che mostrano con che frequenza ciascuna delle seguenti esperienze capitano al suo bambino/ragazzo.</t>
+        </is>
+      </c>
+      <c r="E645" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="646">
+      <c r="A646" s="0">
+        <v>654</v>
+      </c>
+      <c r="B646" s="0">
+        <v>171</v>
+      </c>
+      <c r="C646" s="0">
+        <v>6</v>
+      </c>
+      <c r="D646" s="0" t="inlineStr">
+        <is>
+          <t>Relazione con il bambino/ragazzo</t>
+        </is>
+      </c>
+      <c r="E646" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="647">
+      <c r="A647" s="0">
+        <v>655</v>
+      </c>
+      <c r="B647" s="0">
+        <v>176</v>
+      </c>
+      <c r="C647" s="0">
+        <v>2</v>
+      </c>
+      <c r="D647" s="0" t="inlineStr">
+        <is>
+          <t>Tsiku</t>
+        </is>
+      </c>
+      <c r="E647" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="648">
+      <c r="A648" s="0">
+        <v>656</v>
+      </c>
+      <c r="B648" s="0">
+        <v>176</v>
+      </c>
+      <c r="C648" s="0">
+        <v>1</v>
+      </c>
+      <c r="D648" s="0" t="inlineStr">
+        <is>
+          <t>Dzina/Chizindikiro</t>
+        </is>
+      </c>
+      <c r="E648" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="649">
+      <c r="A649" s="0">
+        <v>657</v>
+      </c>
+      <c r="B649" s="0">
+        <v>176</v>
+      </c>
+      <c r="C649" s="0">
+        <v>4</v>
+      </c>
+      <c r="D649" s="0" t="inlineStr">
+        <is>
+          <t>Chonde zungulizani mawu amene akuwonetsa ndikangazi zinthu izi zachitika kwa inu. Palibe yankho lolondola kapena lokhonza.</t>
+        </is>
+      </c>
+      <c r="E649" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="650">
+      <c r="A650" s="0">
+        <v>658</v>
+      </c>
+      <c r="B650" s="0">
+        <v>156</v>
+      </c>
+      <c r="C650" s="0">
+        <v>2</v>
+      </c>
+      <c r="D650" s="0" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="E650" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="651">
+      <c r="A651" s="0">
+        <v>659</v>
+      </c>
+      <c r="B651" s="0">
+        <v>156</v>
+      </c>
+      <c r="C651" s="0">
+        <v>1</v>
+      </c>
+      <c r="D651" s="0" t="inlineStr">
+        <is>
+          <t>Name/ID:</t>
+        </is>
+      </c>
+      <c r="E651" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="652">
+      <c r="A652" s="0">
+        <v>660</v>
+      </c>
+      <c r="B652" s="0">
+        <v>156</v>
+      </c>
+      <c r="C652" s="0">
+        <v>4</v>
+      </c>
+      <c r="D652" s="0" t="inlineStr">
+        <is>
+          <t>Please put a circle around the word that shows how often each of these things happens for your child.</t>
+        </is>
+      </c>
+      <c r="E652" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="653">
+      <c r="A653" s="0">
+        <v>661</v>
+      </c>
+      <c r="B653" s="0">
+        <v>156</v>
+      </c>
+      <c r="C653" s="0">
+        <v>6</v>
+      </c>
+      <c r="D653" s="0" t="inlineStr">
+        <is>
+          <t>Relationship to Child:</t>
+        </is>
+      </c>
+      <c r="E653" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="654">
+      <c r="A654" s="0">
+        <v>662</v>
+      </c>
+      <c r="B654" s="0">
+        <v>156</v>
+      </c>
+      <c r="C654" s="0">
+        <v>3</v>
+      </c>
+      <c r="D654" s="0" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="E654" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="655">
+      <c r="A655" s="0">
+        <v>663</v>
+      </c>
+      <c r="B655" s="0">
+        <v>157</v>
+      </c>
+      <c r="C655" s="0">
+        <v>2</v>
+      </c>
+      <c r="D655" s="0" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="E655" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="656">
+      <c r="A656" s="0">
+        <v>664</v>
+      </c>
+      <c r="B656" s="0">
+        <v>157</v>
+      </c>
+      <c r="C656" s="0">
+        <v>1</v>
+      </c>
+      <c r="D656" s="0" t="inlineStr">
+        <is>
+          <t>Name/ID:</t>
+        </is>
+      </c>
+      <c r="E656" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="657">
+      <c r="A657" s="0">
+        <v>665</v>
+      </c>
+      <c r="B657" s="0">
+        <v>157</v>
+      </c>
+      <c r="C657" s="0">
+        <v>4</v>
+      </c>
+      <c r="D657" s="0" t="inlineStr">
+        <is>
+          <t>Please put a circle around the word that shows how often each of these things happens for your child.</t>
+        </is>
+      </c>
+      <c r="E657" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="658">
+      <c r="A658" s="0">
+        <v>666</v>
+      </c>
+      <c r="B658" s="0">
+        <v>157</v>
+      </c>
+      <c r="C658" s="0">
+        <v>6</v>
+      </c>
+      <c r="D658" s="0" t="inlineStr">
+        <is>
+          <t>Relationship to Child:</t>
+        </is>
+      </c>
+      <c r="E658" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="659">
+      <c r="A659" s="0">
+        <v>667</v>
+      </c>
+      <c r="B659" s="0">
+        <v>120</v>
+      </c>
+      <c r="C659" s="0">
+        <v>2</v>
+      </c>
+      <c r="D659" s="0" t="inlineStr">
+        <is>
+          <t>তারিখঃ</t>
+        </is>
+      </c>
+      <c r="E659" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="660">
+      <c r="A660" s="0">
+        <v>668</v>
+      </c>
+      <c r="B660" s="0">
+        <v>120</v>
+      </c>
+      <c r="C660" s="0">
+        <v>1</v>
+      </c>
+      <c r="D660" s="0" t="inlineStr">
+        <is>
+          <t>নামঃ</t>
+        </is>
+      </c>
+      <c r="E660" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="661">
+      <c r="A661" s="0">
+        <v>669</v>
+      </c>
+      <c r="B661" s="0">
+        <v>120</v>
+      </c>
+      <c r="C661" s="0">
+        <v>4</v>
+      </c>
+      <c r="D661" s="0" t="inlineStr">
+        <is>
+          <t>নির্দেশনা: নিচের পদ/বাক্যগুলো পড়ে এগুলোর আপনার ক্ষেত্রে কতটুকু ঘন ঘন ঘটে তা নির্দেশ করুন (✓ চিহ্ন দিন)। আপনার উত্তরগুলো সঠিক না ভুল তা নিয়ে চিন্তা করার প্রয়োজন নেই।</t>
+        </is>
+      </c>
+      <c r="E661" s="0">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
